--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--d84208a6-b526-4a2f-8cb0-ed96486ee78a</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--e3fd724d-60dc-44ae-8368-430fd864c236</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--6c96eff6-b80b-4b42-97c0-45f406dc3788</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--c295b42a-8884-4726-a3a6-52ab45ef6277</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--d0cb5cde-f780-4e95-905c-f5ad5056589f</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--2abcd332-7b63-41b1-8e8f-1de018537a13</t>
+    <t>x-mitre-tactic--d2744ec2-ab7d-4b0e-b1e1-6990204f10e6</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--635a0881-b45d-46c8-8877-3cc61bacf5ad</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--559b2ead-8c87-48ac-9871-98fd3973994f</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--0b837347-9f31-4d0a-b4e5-1aa3ff86db96</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--f161027d-2e9d-406e-acc9-b7f38fdd8ef7</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--ef4b1732-aa6f-4808-81de-f3e26f5e8441</t>
   </si>
   <si>
     <t>Закрепление</t>
@@ -97,28 +97,43 @@
     <t>Подготовка к захвату</t>
   </si>
   <si>
-    <t>Colonial Tactic Description</t>
-  </si>
-  <si>
-    <t>https://attack.mitre.org/tactics/TA0005</t>
-  </si>
-  <si>
-    <t>https://attack.mitre.org/tactics/TA0003</t>
-  </si>
-  <si>
-    <t>https://attack.mitre.org/tactics/TA0006</t>
-  </si>
-  <si>
-    <t>https://attack.mitre.org/tactics/TA0001</t>
-  </si>
-  <si>
-    <t>https://attack.mitre.org/tactics/TA0004</t>
-  </si>
-  <si>
-    <t>https://attack.mitre.org/tactics/TA0002</t>
-  </si>
-  <si>
-    <t>21 April 2026</t>
+    <t>Colonial Tactic: Закрепление</t>
+  </si>
+  <si>
+    <t>Colonial Tactic: Захват управления</t>
+  </si>
+  <si>
+    <t>Colonial Tactic: Извлечение выгоды</t>
+  </si>
+  <si>
+    <t>Colonial Tactic: Легитимизация доминирования</t>
+  </si>
+  <si>
+    <t>Colonial Tactic: Нейтрализация защиты</t>
+  </si>
+  <si>
+    <t>Colonial Tactic: Подготовка к захвату</t>
+  </si>
+  <si>
+    <t>https://yugoslavskiy.github.io/tactics/TA0005</t>
+  </si>
+  <si>
+    <t>https://yugoslavskiy.github.io/tactics/TA0003</t>
+  </si>
+  <si>
+    <t>https://yugoslavskiy.github.io/tactics/TA0006</t>
+  </si>
+  <si>
+    <t>https://yugoslavskiy.github.io/tactics/TA0001</t>
+  </si>
+  <si>
+    <t>https://yugoslavskiy.github.io/tactics/TA0004</t>
+  </si>
+  <si>
+    <t>https://yugoslavskiy.github.io/tactics/TA0002</t>
+  </si>
+  <si>
+    <t>27 April 2026</t>
   </si>
   <si>
     <t>russia-colonialism</t>
@@ -515,19 +530,19 @@
         <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -541,22 +556,22 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -570,22 +585,22 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -599,22 +614,22 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -628,22 +643,22 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -657,22 +672,22 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--d2744ec2-ab7d-4b0e-b1e1-6990204f10e6</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--635a0881-b45d-46c8-8877-3cc61bacf5ad</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--559b2ead-8c87-48ac-9871-98fd3973994f</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--0b837347-9f31-4d0a-b4e5-1aa3ff86db96</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--f161027d-2e9d-406e-acc9-b7f38fdd8ef7</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--ef4b1732-aa6f-4808-81de-f3e26f5e8441</t>
+    <t>x-mitre-tactic--db54e8db-f62e-460a-aeae-dc2774109e0b</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--067f052b-c611-409c-bd7e-43d15c74bb71</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--ff3c7c7c-bc24-4b5d-a1d7-2bb3fa94d215</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--375936cc-5321-4887-974e-56d9fc828e4b</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--66a5a58a-877a-45d4-8361-f1176b3e19a3</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--4465cdc8-9417-4b75-b515-e5616119b97f</t>
   </si>
   <si>
     <t>Закрепление</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--db54e8db-f62e-460a-aeae-dc2774109e0b</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--067f052b-c611-409c-bd7e-43d15c74bb71</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--ff3c7c7c-bc24-4b5d-a1d7-2bb3fa94d215</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--375936cc-5321-4887-974e-56d9fc828e4b</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--66a5a58a-877a-45d4-8361-f1176b3e19a3</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--4465cdc8-9417-4b75-b515-e5616119b97f</t>
+    <t>x-mitre-tactic--976cf465-850b-4f52-894f-885ada6a37c0</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--6b1c929e-f46a-479b-986e-888ef65f6bea</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--be9a7b3b-478f-4372-8dd4-cdec07aa0b13</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--cdc5caec-4878-46d0-a054-5051ef27b1e0</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--de60d4f3-1996-43f2-8318-a243cc1d0d14</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--40742d87-6da6-4558-8b1a-b0751ffbb004</t>
   </si>
   <si>
     <t>Закрепление</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--976cf465-850b-4f52-894f-885ada6a37c0</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--6b1c929e-f46a-479b-986e-888ef65f6bea</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--be9a7b3b-478f-4372-8dd4-cdec07aa0b13</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--cdc5caec-4878-46d0-a054-5051ef27b1e0</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--de60d4f3-1996-43f2-8318-a243cc1d0d14</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--40742d87-6da6-4558-8b1a-b0751ffbb004</t>
+    <t>x-mitre-tactic--fe5fc188-eed3-49e3-886a-e7caad0ecc60</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--07a1d89f-04ed-4e3b-a9a8-076cd1ad116d</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--36a279bd-80a6-4456-99fa-9a4de97c2ffb</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--f2d3b0b2-19cf-4f42-8d27-32f6c8bdaa2b</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--9aa9f11a-8cb9-4ca5-aa30-7329a6b5e80f</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--9efb14dd-ae1a-4a9e-810c-765547fbcc0e</t>
   </si>
   <si>
     <t>Закрепление</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--fe5fc188-eed3-49e3-886a-e7caad0ecc60</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--07a1d89f-04ed-4e3b-a9a8-076cd1ad116d</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--36a279bd-80a6-4456-99fa-9a4de97c2ffb</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--f2d3b0b2-19cf-4f42-8d27-32f6c8bdaa2b</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--9aa9f11a-8cb9-4ca5-aa30-7329a6b5e80f</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--9efb14dd-ae1a-4a9e-810c-765547fbcc0e</t>
+    <t>x-mitre-tactic--9cad3760-6233-4d69-a3ca-1d8a18bc9828</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--a5ebc217-416f-4512-a118-73f1f7e3d76b</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--7efb6f09-3729-4ca8-8175-8782a33cd530</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--93f3e3b2-80e7-44aa-ae33-07c33c651090</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--60599f15-5a6c-4d18-b3a8-53fb0b8f85ad</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--7357e3fb-9ecd-4e2d-82ae-6336c8a4ede3</t>
   </si>
   <si>
     <t>Закрепление</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--9cad3760-6233-4d69-a3ca-1d8a18bc9828</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--a5ebc217-416f-4512-a118-73f1f7e3d76b</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--7efb6f09-3729-4ca8-8175-8782a33cd530</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--93f3e3b2-80e7-44aa-ae33-07c33c651090</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--60599f15-5a6c-4d18-b3a8-53fb0b8f85ad</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--7357e3fb-9ecd-4e2d-82ae-6336c8a4ede3</t>
+    <t>x-mitre-tactic--070941d3-3443-4e16-baea-5a8e95afb1d1</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--39a78f48-952f-4914-9a7f-2fa9141a1bf2</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--503557f9-bc68-415d-93de-17640a30099c</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--b597c77e-caae-4737-9194-8a0f58369481</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--7c425835-87cc-4a18-bb23-e0cb3a47e5ac</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--e05d8689-8aad-45e0-91df-3d93c47c0e6d</t>
   </si>
   <si>
     <t>Закрепление</t>

--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-tactics.xlsx
@@ -61,22 +61,22 @@
     <t>TA0002</t>
   </si>
   <si>
-    <t>x-mitre-tactic--070941d3-3443-4e16-baea-5a8e95afb1d1</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--39a78f48-952f-4914-9a7f-2fa9141a1bf2</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--503557f9-bc68-415d-93de-17640a30099c</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--b597c77e-caae-4737-9194-8a0f58369481</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--7c425835-87cc-4a18-bb23-e0cb3a47e5ac</t>
-  </si>
-  <si>
-    <t>x-mitre-tactic--e05d8689-8aad-45e0-91df-3d93c47c0e6d</t>
+    <t>x-mitre-tactic--04470a51-a94f-4d78-8a0c-f4774e1d6ca5</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--67655caf-a53b-4481-8763-1500b1335b0b</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--f95402de-572c-49eb-bd02-26e530ce2baf</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--e631ee1b-e639-433e-b3e0-188d44bc8843</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--45abea34-e7c2-44e3-ae97-f361ad66165d</t>
+  </si>
+  <si>
+    <t>x-mitre-tactic--0452af01-1ea2-4acf-8308-28502e85a4fd</t>
   </si>
   <si>
     <t>Закрепление</t>
@@ -133,7 +133,7 @@
     <t>https://yugoslavskiy.github.io/tactics/TA0002</t>
   </si>
   <si>
-    <t>27 April 2026</t>
+    <t>29 April 2026</t>
   </si>
   <si>
     <t>russia-colonialism</t>
